--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-30.xlsx
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
         <v>1.58</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>1.01</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
         <v>1.97</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
         <v>1.01</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G13" t="n">
         <v>2.12</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -3905,19 +3905,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G14" t="n">
         <v>4.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="I14" t="n">
         <v>2.14</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
         <v>3.9</v>
@@ -3935,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
         <v>1.9</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G19" t="n">
         <v>2.18</v>
@@ -5184,7 +5184,7 @@
         <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J19" t="n">
         <v>3.15</v>
@@ -5196,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.48</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5432,7 +5432,7 @@
         <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H20" t="n">
         <v>2.16</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5683,16 +5683,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="G21" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
         <v>3.65</v>
@@ -5713,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
         <v>1.96</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -5940,10 +5940,10 @@
         <v>1.58</v>
       </c>
       <c r="G22" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I22" t="n">
         <v>7.2</v>
@@ -5970,7 +5970,7 @@
         <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -6448,16 +6448,16 @@
         <v>1.01</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>1.3</v>
       </c>
       <c r="H24" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
       </c>
       <c r="J24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="K24" t="n">
         <v>950</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="J25" t="n">
-        <v>1.02</v>
+        <v>2.74</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
         <v>5.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K28" t="n">
         <v>3.7</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
         <v>4.8</v>
       </c>
       <c r="H29" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="I29" t="n">
         <v>2.1</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q32" t="n">
         <v>2.44</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9272,7 @@
         <v>1.93</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -9750,10 +9750,10 @@
         <v>1.65</v>
       </c>
       <c r="G37" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H37" t="n">
-        <v>1.09</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
         <v>7.8</v>
@@ -9780,7 +9780,7 @@
         <v>1.75</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>
@@ -10004,16 +10004,16 @@
         <v>2.32</v>
       </c>
       <c r="G38" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H38" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="I38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J38" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K38" t="n">
         <v>4.1</v>
@@ -10031,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-28 01:43:12</t>
+          <t>2026-05-28 03:55:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB38"/>
+  <dimension ref="A1:CB43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>07:00:00</t>
+          <t>04:30:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Yongin FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Daegu Fc</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>5.3</v>
       </c>
       <c r="H2" t="n">
-        <v>2.82</v>
+        <v>1.82</v>
       </c>
       <c r="I2" t="n">
-        <v>2.96</v>
+        <v>1.97</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
       </c>
       <c r="K2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X2" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH2" t="n">
         <v>3.85</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chinese League 1</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,234 +1097,234 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>04:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Chungnam Asan</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X3" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS3" t="n">
         <v>1.01</v>
       </c>
-      <c r="G3" t="n">
+      <c r="AT3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>1000</v>
       </c>
-      <c r="H3" t="n">
+      <c r="BK3" t="n">
         <v>1.01</v>
       </c>
-      <c r="I3" t="n">
+      <c r="BL3" t="n">
         <v>1000</v>
       </c>
-      <c r="J3" t="n">
+      <c r="BM3" t="n">
         <v>1.01</v>
       </c>
-      <c r="K3" t="n">
-        <v>950</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="BN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>1.01</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Chinese League 1</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,234 +1351,234 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>04:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dalian Kun City FC</t>
+          <t>Busan IPark</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shijiazhuang Gongfu FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="X4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL4" t="n">
         <v>1000</v>
       </c>
-      <c r="H4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="BM4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR4" t="n">
         <v>1000</v>
       </c>
-      <c r="J4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K4" t="n">
-        <v>950</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -1605,36 +1605,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Henan Songshan Longmen</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhejiang Greentown</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.86</v>
+        <v>2.44</v>
       </c>
       <c r="G5" t="n">
-        <v>1.97</v>
+        <v>2.66</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="I5" t="n">
-        <v>5.1</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,36 +1859,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ishoj IF</t>
+          <t>Suwon FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VSK Aarhus FC</t>
+          <t>Seongnam FC</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>South Korean K2 League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,36 +2113,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>07:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Helsingor</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brabrand</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>1.82</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>08:15:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FC Dziugas</t>
+          <t>FC Helsingor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Panevezys</t>
+          <t>Brabrand</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Ishoj IF</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trans Narva</t>
+          <t>VSK Aarhus FC</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,36 +2875,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus</t>
+          <t>Henan Songshan Longmen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Nomme Kalju</t>
+          <t>Zhejiang Greentown</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.97</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2919,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -3129,36 +3129,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Dalian Kun City FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jiangxi Dingnan United</t>
+          <t>Shijiazhuang Gongfu FC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -3383,36 +3383,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Foshan Nanshi FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="H12" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -3620,14 +3620,14 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3637,36 +3637,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>08:35:00</t>
+          <t>08:15:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chengdu Rongcheng</t>
+          <t>FC Dziugas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shandong Taishan</t>
+          <t>Panevezys</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="G13" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3681,10 +3681,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3874,14 +3874,14 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3891,55 +3891,55 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Chongqing Tonglianglong</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Jiangxi Dingnan United</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="H14" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="I14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2.14</v>
       </c>
-      <c r="J14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.9</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Chinese Super League</t>
+          <t>Chinese League 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4145,36 +4145,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Shenzhen Peng City</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qingdao Hainiu</t>
+          <t>Foshan Nanshi FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="G15" t="n">
-        <v>2.34</v>
+        <v>1.76</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4189,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -4382,14 +4382,14 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Danish 2nd Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4399,36 +4399,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>HIK Hellerup</t>
+          <t>Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vendsyssel FF</t>
+          <t>Nomme Kalju</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>1.56</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -4636,14 +4636,14 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4653,36 +4653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>09:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Liepajas Metalurgs</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Tukums 2000</t>
+          <t>Trans Narva</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>5.9</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lithuanian A Lyga</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4907,36 +4907,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>08:35:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FK Banga Gargzdu</t>
+          <t>Chengdu Rongcheng</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fk Siauliai</t>
+          <t>Shandong Taishan</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.12</v>
       </c>
       <c r="H18" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -5144,14 +5144,14 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5161,42 +5161,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Racing Club (Uru)</t>
+          <t>HIK Hellerup</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Defensor Sporting</t>
+          <t>Vendsyssel FF</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="G19" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="I19" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5205,10 +5205,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -5398,14 +5398,14 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5415,36 +5415,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Liepajas Metalurgs</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>FK Tukums 2000</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="G20" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="I20" t="n">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -5459,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.36</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -5652,14 +5652,14 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5669,33 +5669,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Chongqing Tonglianglong</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kalmar FF</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.88</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>1.97</v>
+        <v>4.4</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>1.98</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>2.16</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
         <v>3.9</v>
@@ -5713,10 +5713,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -5906,14 +5906,14 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Swedish Allsvenskan</t>
+          <t>Chinese Super League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5923,36 +5923,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Malmo FF</t>
+          <t>Shenzhen Peng City</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Halmstads</t>
+          <t>Qingdao Hainiu</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.58</v>
+        <v>2.16</v>
       </c>
       <c r="G22" t="n">
-        <v>1.63</v>
+        <v>2.34</v>
       </c>
       <c r="H22" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="I22" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -5967,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -6160,14 +6160,14 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Lithuanian A Lyga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6177,36 +6177,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tammeka Tartu</t>
+          <t>FK Banga Gargzdu</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FCI Tallinn</t>
+          <t>Fk Siauliai</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>1.81</v>
       </c>
       <c r="H23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -6221,10 +6221,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -6414,14 +6414,14 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6431,36 +6431,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FK Auda</t>
+          <t>Malmo FF</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Halmstads</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="G24" t="n">
-        <v>1.3</v>
+        <v>1.63</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
         <v>4.3</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -6475,10 +6475,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -6668,14 +6668,14 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6685,37 +6685,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lillestrom</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kalmar FF</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.96</v>
+        <v>1.88</v>
       </c>
       <c r="G25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.9</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
@@ -6729,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -6922,14 +6922,14 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Swedish Allsvenskan</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6939,55 +6939,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1.63</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H26" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.57</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -7176,14 +7176,14 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -7193,42 +7193,42 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Asociacion Deportiva Tarma</t>
+          <t>Racing Club (Uru)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>Defensor Sporting</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -7237,10 +7237,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -7430,14 +7430,14 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7447,36 +7447,36 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Tammeka Tartu</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>FCI Tallinn</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="G28" t="n">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="I28" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -7491,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -7684,14 +7684,14 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7701,36 +7701,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>FK Auda</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Colo Colo</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="G29" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="H29" t="n">
-        <v>1.94</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -7745,10 +7745,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.85</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -7938,14 +7938,14 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7955,36 +7955,36 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Lillestrom</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G30" t="n">
         <v>1000</v>
       </c>
       <c r="H30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
         <v>1000</v>
       </c>
       <c r="J30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K30" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
         <v>1.01</v>
@@ -8192,14 +8192,14 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -8209,36 +8209,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.34</v>
+        <v>1.63</v>
       </c>
       <c r="G31" t="n">
-        <v>2.6</v>
+        <v>1.72</v>
       </c>
       <c r="H31" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -8253,10 +8253,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -8463,36 +8463,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Asociacion Deportiva Tarma</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Cusco FC</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -8507,10 +8507,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -8700,14 +8700,14 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -8717,36 +8717,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juan Pablo II College</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -8761,10 +8761,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -8971,36 +8971,36 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -9015,10 +9015,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -9208,14 +9208,14 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -9225,36 +9225,36 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportes Concepcion</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.53</v>
+        <v>2.34</v>
       </c>
       <c r="G35" t="n">
-        <v>1.61</v>
+        <v>2.58</v>
       </c>
       <c r="H35" t="n">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="K35" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -9269,10 +9269,10 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
@@ -9479,36 +9479,36 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="G36" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="H36" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="I36" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -9523,10 +9523,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -9716,14 +9716,14 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9733,36 +9733,36 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sport Boys (Per)</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Comerciantes Unidos</t>
+          <t>Colo Colo</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.65</v>
+        <v>4.1</v>
       </c>
       <c r="G37" t="n">
-        <v>1.79</v>
+        <v>4.7</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>1.92</v>
       </c>
       <c r="I37" t="n">
-        <v>7.8</v>
+        <v>2.1</v>
       </c>
       <c r="J37" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K37" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -9777,10 +9777,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -9970,14 +9970,14 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9987,36 +9987,36 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Juan Pablo II College</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10031,7 +10031,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="Q38" t="n">
         <v>1.01</v>
@@ -10224,7 +10224,1277 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-28 03:55:59</t>
+          <t>2026-05-28 06:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Fortaleza EC</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB39" t="inlineStr">
+        <is>
+          <t>2026-05-28 06:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Deportes Concepcion</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="inlineStr">
+        <is>
+          <t>2026-05-28 06:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Atletico Ottawa</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB41" t="inlineStr">
+        <is>
+          <t>2026-05-28 06:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Peruvian Primera Division</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sport Boys (Per)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB42" t="inlineStr">
+        <is>
+          <t>2026-05-28 06:09:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sport Recife</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I43" t="n">
+        <v>100</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K43" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB43" t="inlineStr">
+        <is>
+          <t>2026-05-28 06:09:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB68"/>
+  <dimension ref="A1:CB70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>4.2</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="n">
         <v>1.82</v>
@@ -875,34 +875,34 @@
         <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="O2" t="n">
         <v>1.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
         <v>1.71</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
         <v>2.02</v>
@@ -1022,7 +1022,7 @@
         <v>3.85</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -1111,16 +1111,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H3" t="n">
         <v>1.99</v>
       </c>
       <c r="I3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J3" t="n">
         <v>3.5</v>
@@ -1159,7 +1159,7 @@
         <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="W3" t="n">
         <v>1.29</v>
@@ -1276,7 +1276,7 @@
         <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
         <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
         <v>1.82</v>
@@ -1422,7 +1422,7 @@
         <v>15</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z4" t="n">
         <v>55</v>
@@ -1431,7 +1431,7 @@
         <v>190</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
@@ -1446,10 +1446,10 @@
         <v>12</v>
       </c>
       <c r="AG4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
         <v>110</v>
@@ -1479,10 +1479,10 @@
         <v>12.5</v>
       </c>
       <c r="AR4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS4" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.9</v>
       </c>
       <c r="AT4" t="n">
         <v>5.9</v>
@@ -1494,7 +1494,7 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AX4" t="n">
         <v>7.6</v>
@@ -1506,7 +1506,7 @@
         <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BB4" t="n">
         <v>13.5</v>
@@ -1515,22 +1515,22 @@
         <v>14</v>
       </c>
       <c r="BD4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE4" t="n">
         <v>4.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BH4" t="n">
         <v>3.4</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="BJ4" t="n">
         <v>11</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1646,13 +1646,13 @@
         <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
         <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="R5" t="n">
         <v>1.5</v>
@@ -1781,22 +1781,22 @@
         <v>15.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BJ5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BN5" t="n">
         <v>5.5</v>
@@ -1805,44 +1805,44 @@
         <v>4.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV5" t="n">
         <v>23</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX5" t="n">
         <v>30</v>
       </c>
       <c r="BY5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
         <v>19</v>
       </c>
       <c r="CA5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G6" t="n">
         <v>2.5</v>
@@ -1882,7 +1882,7 @@
         <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
         <v>3.1</v>
@@ -1891,7 +1891,7 @@
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1900,13 +1900,13 @@
         <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
         <v>1.91</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.34</v>
@@ -2038,7 +2038,7 @@
         <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -2130,13 +2130,13 @@
         <v>5.2</v>
       </c>
       <c r="G7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H7" t="n">
         <v>1.68</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
@@ -2178,7 +2178,7 @@
         <v>2.24</v>
       </c>
       <c r="W7" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -2310,7 +2310,7 @@
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -2390,10 +2390,10 @@
         <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J8" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="K8" t="n">
         <v>3.3</v>
@@ -2408,7 +2408,7 @@
         <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="P8" t="n">
         <v>1.49</v>
@@ -2429,7 +2429,7 @@
         <v>1.74</v>
       </c>
       <c r="V8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W8" t="n">
         <v>1.33</v>
@@ -2462,13 +2462,13 @@
         <v>28</v>
       </c>
       <c r="AG8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AH8" t="n">
         <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
         <v>85</v>
@@ -2483,64 +2483,64 @@
         <v>230</v>
       </c>
       <c r="AN8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AO8" t="n">
         <v>48</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AY8" t="n">
         <v>4.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BA8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BE8" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BF8" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BH8" t="n">
         <v>2.74</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -2635,19 +2635,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G9" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
         <v>3.85</v>
@@ -2659,7 +2659,7 @@
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>1.42</v>
@@ -2668,25 +2668,25 @@
         <v>1.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R9" t="n">
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
         <v>2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V9" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="X9" t="n">
         <v>13</v>
@@ -2704,7 +2704,7 @@
         <v>8</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD9" t="n">
         <v>27</v>
@@ -2749,10 +2749,10 @@
         <v>4</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
         <v>3.15</v>
@@ -2761,22 +2761,22 @@
         <v>3.35</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AW9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY9" t="n">
         <v>3.6</v>
       </c>
-      <c r="AY9" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB9" t="n">
         <v>4.2</v>
@@ -2785,16 +2785,16 @@
         <v>4.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF9" t="n">
         <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="n">
         <v>3.05</v>
@@ -2806,59 +2806,59 @@
         <v>11.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BN9" t="n">
         <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BP9" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BT9" t="n">
         <v>9</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BZ9" t="n">
         <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G10" t="n">
         <v>1.97</v>
@@ -2898,7 +2898,7 @@
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
         <v>4</v>
@@ -2910,19 +2910,19 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="R10" t="n">
         <v>1.57</v>
@@ -2937,7 +2937,7 @@
         <v>2.42</v>
       </c>
       <c r="V10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
         <v>2.02</v>
@@ -2988,67 +2988,67 @@
         <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO10" t="n">
         <v>42</v>
       </c>
       <c r="AP10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS10" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AT10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW10" t="n">
         <v>4</v>
       </c>
-      <c r="AR10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AX10" t="n">
-        <v>3.75</v>
+        <v>10</v>
       </c>
       <c r="AY10" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BB10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BF10" t="n">
         <v>6.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
         <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
@@ -3191,7 +3191,7 @@
         <v>1.98</v>
       </c>
       <c r="V11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="W11" t="n">
         <v>1.2</v>
@@ -3209,7 +3209,7 @@
         <v>20</v>
       </c>
       <c r="AB11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AC11" t="n">
         <v>9.199999999999999</v>
@@ -3227,7 +3227,7 @@
         <v>22</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>38</v>
@@ -3302,13 +3302,13 @@
         <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH11" t="n">
         <v>3.55</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BJ11" t="n">
         <v>10.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -3421,13 +3421,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q12" t="n">
         <v>1.23</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
         <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -4673,10 +4673,10 @@
         <v>2.2</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.25</v>
@@ -4685,10 +4685,10 @@
         <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
         <v>3.3</v>
@@ -4697,16 +4697,16 @@
         <v>1.35</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
         <v>1.85</v>
@@ -4715,7 +4715,7 @@
         <v>1.96</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
         <v>1.84</v>
@@ -4832,7 +4832,7 @@
         <v>3.35</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="BJ17" t="n">
         <v>10.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4921,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G18" t="n">
         <v>3.9</v>
       </c>
       <c r="H18" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="I18" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="J18" t="n">
         <v>2.88</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -4969,10 +4969,10 @@
         <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="W18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X18" t="n">
         <v>16</v>
@@ -5029,7 +5029,7 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>7.4</v>
+        <v>2</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.94</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -5178,13 +5178,13 @@
         <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
@@ -5208,7 +5208,7 @@
         <v>1.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="R19" t="n">
         <v>1.18</v>
@@ -5223,10 +5223,10 @@
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
         <v>16</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
         <v>1.53</v>
       </c>
       <c r="J20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K20" t="n">
         <v>5.6</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
         <v>2.12</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I22" t="n">
         <v>3.6</v>
@@ -5970,7 +5970,7 @@
         <v>2.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R22" t="n">
         <v>1.73</v>
@@ -6009,7 +6009,7 @@
         <v>11.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE22" t="n">
         <v>34</v>
@@ -6021,52 +6021,52 @@
         <v>12</v>
       </c>
       <c r="AH22" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI22" t="n">
         <v>34</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
         <v>19</v>
       </c>
       <c r="AL22" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AM22" t="n">
         <v>50</v>
       </c>
       <c r="AN22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP22" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ22" t="n">
         <v>19.5</v>
       </c>
       <c r="AR22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS22" t="n">
         <v>7.6</v>
       </c>
-      <c r="AS22" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AT22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU22" t="n">
         <v>9.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AX22" t="n">
         <v>15</v>
@@ -6075,13 +6075,13 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="BB22" t="n">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="BC22" t="n">
         <v>16</v>
@@ -6090,13 +6090,13 @@
         <v>21</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF22" t="n">
         <v>6.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BH22" t="n">
         <v>1000</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G23" t="n">
         <v>4.5</v>
@@ -6200,7 +6200,7 @@
         <v>1.94</v>
       </c>
       <c r="I23" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J23" t="n">
         <v>3.7</v>
@@ -6224,7 +6224,7 @@
         <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R23" t="n">
         <v>1.38</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -6454,7 +6454,7 @@
         <v>3.9</v>
       </c>
       <c r="I24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J24" t="n">
         <v>3.65</v>
@@ -6493,7 +6493,7 @@
         <v>2.18</v>
       </c>
       <c r="V24" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W24" t="n">
         <v>1.92</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -6959,7 +6959,7 @@
         <v>1.26</v>
       </c>
       <c r="H26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="I26" t="n">
         <v>15.5</v>
@@ -6968,7 +6968,7 @@
         <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -6983,10 +6983,10 @@
         <v>1.16</v>
       </c>
       <c r="P26" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R26" t="n">
         <v>1.75</v>
@@ -7007,7 +7007,7 @@
         <v>4.8</v>
       </c>
       <c r="X26" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y26" t="n">
         <v>60</v>
@@ -7028,10 +7028,10 @@
         <v>55</v>
       </c>
       <c r="AE26" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AF26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="n">
         <v>14.5</v>
@@ -7046,13 +7046,13 @@
         <v>11.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL26" t="n">
         <v>46</v>
       </c>
       <c r="AM26" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN26" t="n">
         <v>3.75</v>
@@ -7061,16 +7061,16 @@
         <v>330</v>
       </c>
       <c r="AP26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>34</v>
-      </c>
       <c r="AR26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS26" t="n">
         <v>6</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>6.2</v>
       </c>
       <c r="AT26" t="n">
         <v>8.4</v>
@@ -7079,22 +7079,22 @@
         <v>12</v>
       </c>
       <c r="AV26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AX26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY26" t="n">
         <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BA26" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BB26" t="n">
         <v>7.4</v>
@@ -7103,16 +7103,16 @@
         <v>10</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BH26" t="n">
         <v>1000</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -7464,13 +7464,13 @@
         <v>1.56</v>
       </c>
       <c r="G28" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="H28" t="n">
         <v>6.2</v>
       </c>
       <c r="I28" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J28" t="n">
         <v>3.85</v>
@@ -7497,7 +7497,7 @@
         <v>1.91</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
         <v>2.72</v>
@@ -7509,10 +7509,10 @@
         <v>1.85</v>
       </c>
       <c r="V28" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W28" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X28" t="n">
         <v>18</v>
@@ -7548,7 +7548,7 @@
         <v>29</v>
       </c>
       <c r="AI28" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ28" t="n">
         <v>19</v>
@@ -7581,7 +7581,7 @@
         <v>4.3</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -7960,239 +7960,239 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sundsvall</t>
+          <t>Falkenbergs</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="G30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
         <v>3.35</v>
       </c>
-      <c r="H30" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.54</v>
-      </c>
       <c r="J30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>1.98</v>
       </c>
       <c r="O30" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P30" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="T30" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="W30" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="X30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y30" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="AA30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AD30" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AE30" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
         <v>23</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AI30" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AK30" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AL30" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ30" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR30" t="n">
         <v>14</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT30" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW30" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AX30" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AY30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ30" t="n">
         <v>12</v>
       </c>
-      <c r="AZ30" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB30" t="n">
+      <c r="BK30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>24</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BR30" t="n">
         <v>38</v>
       </c>
-      <c r="BC30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD30" t="n">
+      <c r="BS30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BV30" t="n">
         <v>32</v>
       </c>
-      <c r="BE30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BJ30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BK30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BN30" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP30" t="n">
-        <v>36</v>
-      </c>
-      <c r="BQ30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BR30" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BT30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BU30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BV30" t="n">
-        <v>26</v>
-      </c>
       <c r="BW30" t="n">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="BX30" t="n">
         <v>46</v>
       </c>
       <c r="BY30" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="BZ30" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="CA30" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
         <v>3.45</v>
       </c>
       <c r="H31" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I31" t="n">
         <v>2.3</v>
@@ -8241,7 +8241,7 @@
         <v>4.1</v>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
         <v>1.04</v>
@@ -8259,13 +8259,13 @@
         <v>1.63</v>
       </c>
       <c r="R31" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S31" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T31" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="U31" t="n">
         <v>2.48</v>
@@ -8292,7 +8292,7 @@
         <v>20</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD31" t="n">
         <v>13.5</v>
@@ -8325,13 +8325,13 @@
         <v>75</v>
       </c>
       <c r="AN31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO31" t="n">
         <v>14.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AQ31" t="n">
         <v>10.5</v>
@@ -8340,13 +8340,13 @@
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="AT31" t="n">
         <v>13</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV31" t="n">
         <v>8.800000000000001</v>
@@ -8364,25 +8364,25 @@
         <v>11.5</v>
       </c>
       <c r="BA31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB31" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB31" t="n">
-        <v>5</v>
-      </c>
       <c r="BC31" t="n">
-        <v>24</v>
+        <v>4.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BF31" t="n">
         <v>18</v>
       </c>
       <c r="BG31" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH31" t="n">
         <v>1000</v>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -8480,16 +8480,16 @@
         <v>1.94</v>
       </c>
       <c r="G32" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K32" t="n">
         <v>3.8</v>
@@ -8510,7 +8510,7 @@
         <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R32" t="n">
         <v>1.37</v>
@@ -8528,37 +8528,37 @@
         <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AA32" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB32" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC32" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AE32" t="n">
         <v>60</v>
       </c>
       <c r="AF32" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH32" t="n">
         <v>23</v>
@@ -8567,73 +8567,73 @@
         <v>70</v>
       </c>
       <c r="AJ32" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK32" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL32" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM32" t="n">
         <v>130</v>
       </c>
       <c r="AN32" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP32" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AS32" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AT32" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW32" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="AX32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY32" t="n">
         <v>10</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9</v>
       </c>
       <c r="AZ32" t="n">
         <v>16.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BB32" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE32" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG32" t="n">
         <v>46</v>
@@ -8642,34 +8642,34 @@
         <v>1000</v>
       </c>
       <c r="BI32" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BJ32" t="n">
         <v>13.5</v>
       </c>
       <c r="BK32" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
       </c>
       <c r="BM32" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="BN32" t="n">
         <v>6</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BP32" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>8.4</v>
+        <v>1.45</v>
       </c>
       <c r="BR32" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS32" t="n">
         <v>1.57</v>
@@ -8678,29 +8678,29 @@
         <v>1000</v>
       </c>
       <c r="BU32" t="n">
-        <v>5.2</v>
+        <v>1.57</v>
       </c>
       <c r="BV32" t="n">
         <v>50</v>
       </c>
       <c r="BW32" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BX32" t="n">
         <v>1000</v>
       </c>
       <c r="BY32" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="BZ32" t="n">
         <v>32</v>
       </c>
       <c r="CA32" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -8722,239 +8722,239 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Falkenbergs</t>
+          <t>Sundsvall</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.36</v>
+        <v>3.05</v>
       </c>
       <c r="G33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I33" t="n">
         <v>2.54</v>
       </c>
-      <c r="H33" t="n">
-        <v>3</v>
-      </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S33" t="n">
         <v>3.35</v>
       </c>
-      <c r="J33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.01</v>
-      </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="W33" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="X33" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y33" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB33" t="n">
         <v>15.5</v>
       </c>
       <c r="AC33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT33" t="n">
         <v>11</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AU33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW33" t="n">
         <v>19</v>
       </c>
-      <c r="AE33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK33" t="n">
+      <c r="AX33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>9</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP33" t="n">
         <v>36</v>
       </c>
-      <c r="AL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY33" t="n">
+      <c r="BQ33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BT33" t="n">
         <v>7.6</v>
       </c>
-      <c r="AZ33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ33" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN33" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BP33" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BR33" t="n">
-        <v>38</v>
-      </c>
-      <c r="BS33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BT33" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BU33" t="n">
-        <v>1.61</v>
+        <v>3.55</v>
       </c>
       <c r="BV33" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="BW33" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="BX33" t="n">
         <v>46</v>
       </c>
       <c r="BY33" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="BZ33" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="CA33" t="n">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -9018,13 +9018,13 @@
         <v>2.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="R34" t="n">
         <v>1.25</v>
       </c>
       <c r="S34" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -9033,7 +9033,7 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W34" t="n">
         <v>1.34</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
         <v>3.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K35" t="n">
         <v>4.4</v>
@@ -9281,13 +9281,13 @@
         <v>2.32</v>
       </c>
       <c r="T35" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
         <v>2.3</v>
       </c>
       <c r="V35" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W35" t="n">
         <v>1.65</v>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -9502,19 +9502,19 @@
         <v>7.8</v>
       </c>
       <c r="I36" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="J36" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="K36" t="n">
         <v>6.2</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N36" t="n">
         <v>5.7</v>
@@ -9523,16 +9523,16 @@
         <v>1.17</v>
       </c>
       <c r="P36" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Q36" t="n">
         <v>1.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S36" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T36" t="n">
         <v>1.77</v>
@@ -9547,7 +9547,7 @@
         <v>3.15</v>
       </c>
       <c r="X36" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="Y36" t="n">
         <v>38</v>
@@ -9559,37 +9559,37 @@
         <v>300</v>
       </c>
       <c r="AB36" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AC36" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD36" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AE36" t="n">
         <v>130</v>
       </c>
       <c r="AF36" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AH36" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI36" t="n">
         <v>110</v>
       </c>
       <c r="AJ36" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AL36" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AM36" t="n">
         <v>120</v>
@@ -9604,119 +9604,119 @@
         <v>20</v>
       </c>
       <c r="AQ36" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="AR36" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="AS36" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU36" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AU36" t="n">
-        <v>11</v>
-      </c>
       <c r="AV36" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX36" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AZ36" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB36" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BC36" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF36" t="n">
         <v>3.7</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH36" t="n">
-        <v>6.2</v>
+        <v>4.8</v>
       </c>
       <c r="BI36" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="BJ36" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>6</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>21</v>
+      </c>
+      <c r="BS36" t="n">
         <v>6.8</v>
       </c>
-      <c r="BL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BN36" t="n">
+      <c r="BT36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BU36" t="n">
         <v>5.5</v>
       </c>
-      <c r="BO36" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BP36" t="n">
-        <v>11</v>
-      </c>
-      <c r="BQ36" t="n">
+      <c r="BV36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX36" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BZ36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="CA36" t="n">
         <v>5.3</v>
       </c>
-      <c r="BR36" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS36" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BT36" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BU36" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BV36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BX36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BZ36" t="n">
-        <v>15</v>
-      </c>
-      <c r="CA36" t="n">
-        <v>7.2</v>
-      </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -9756,13 +9756,13 @@
         <v>6.4</v>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J37" t="n">
         <v>4.5</v>
       </c>
       <c r="K37" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L37" t="n">
         <v>1.34</v>
@@ -9774,34 +9774,34 @@
         <v>4.3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P37" t="n">
         <v>2.14</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R37" t="n">
         <v>1.45</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T37" t="n">
         <v>1.9</v>
       </c>
       <c r="U37" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V37" t="n">
         <v>1.16</v>
       </c>
       <c r="W37" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="X37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y37" t="n">
         <v>28</v>
@@ -9813,10 +9813,10 @@
         <v>240</v>
       </c>
       <c r="AB37" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD37" t="n">
         <v>32</v>
@@ -9825,7 +9825,7 @@
         <v>120</v>
       </c>
       <c r="AF37" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AG37" t="n">
         <v>12.5</v>
@@ -9855,31 +9855,31 @@
         <v>140</v>
       </c>
       <c r="AP37" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ37" t="n">
         <v>20</v>
       </c>
       <c r="AR37" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT37" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU37" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX37" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY37" t="n">
         <v>9</v>
@@ -9888,25 +9888,25 @@
         <v>20</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC37" t="n">
         <v>14</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF37" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BH37" t="n">
         <v>1000</v>
@@ -9930,7 +9930,7 @@
         <v>5.6</v>
       </c>
       <c r="BO37" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="BP37" t="n">
         <v>14.5</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -10025,13 +10025,13 @@
         <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O38" t="n">
         <v>1.2</v>
       </c>
       <c r="P38" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q38" t="n">
         <v>1.2</v>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -10246,12 +10246,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FC Trollhattan</t>
+          <t>Hassleholms IF</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aatvidabergs Ff</t>
+          <t>Utsiktens</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -10279,22 +10279,22 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O39" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P39" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="R39" t="n">
         <v>1.24</v>
       </c>
       <c r="S39" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -10533,13 +10533,13 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O40" t="n">
         <v>1.05</v>
       </c>
       <c r="P40" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q40" t="n">
         <v>1.24</v>
@@ -10617,52 +10617,52 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O41" t="n">
         <v>1.16</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -11041,13 +11041,13 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O42" t="n">
         <v>1.13</v>
       </c>
       <c r="P42" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q42" t="n">
         <v>1.13</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -11289,7 +11289,7 @@
         <v>4.9</v>
       </c>
       <c r="L43" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="M43" t="n">
         <v>1.03</v>
@@ -11370,7 +11370,7 @@
         <v>32</v>
       </c>
       <c r="AM43" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AN43" t="n">
         <v>7</v>
@@ -11385,10 +11385,10 @@
         <v>18.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT43" t="n">
         <v>9.4</v>
@@ -11400,19 +11400,19 @@
         <v>15.5</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AX43" t="n">
         <v>9.6</v>
       </c>
       <c r="AY43" t="n">
-        <v>8</v>
+        <v>3.85</v>
       </c>
       <c r="AZ43" t="n">
         <v>13.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB43" t="n">
         <v>13</v>
@@ -11430,7 +11430,7 @@
         <v>5.4</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH43" t="n">
         <v>4.5</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G44" t="n">
         <v>1000</v>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -11770,12 +11770,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Hassleholms IF</t>
+          <t>FC Trollhattan</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Utsiktens</t>
+          <t>Aatvidabergs Ff</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -11806,19 +11806,19 @@
         <v>1.26</v>
       </c>
       <c r="O45" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="P45" t="n">
         <v>1.26</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="R45" t="n">
         <v>1.24</v>
       </c>
       <c r="S45" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12036,7 @@
         <v>2.86</v>
       </c>
       <c r="G46" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H46" t="n">
         <v>2.16</v>
@@ -12057,10 +12057,10 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>2.68</v>
+        <v>5.5</v>
       </c>
       <c r="O46" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P46" t="n">
         <v>2.66</v>
@@ -12069,10 +12069,10 @@
         <v>1.48</v>
       </c>
       <c r="R46" t="n">
-        <v>1.27</v>
+        <v>1.66</v>
       </c>
       <c r="S46" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
@@ -12084,7 +12084,7 @@
         <v>1.7</v>
       </c>
       <c r="W46" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X46" t="n">
         <v>36</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12562,7 @@
         <v>1.29</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N48" t="n">
         <v>2.18</v>
@@ -12580,7 +12580,7 @@
         <v>1.44</v>
       </c>
       <c r="S48" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T48" t="n">
         <v>1.48</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
         <v>2.92</v>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J49" t="n">
         <v>3.2</v>
@@ -12813,16 +12813,16 @@
         <v>3.5</v>
       </c>
       <c r="L49" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M49" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N49" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O49" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P49" t="n">
         <v>1.75</v>
@@ -12831,16 +12831,16 @@
         <v>2.12</v>
       </c>
       <c r="R49" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S49" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="T49" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="U49" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
         <v>1.45</v>
@@ -12849,176 +12849,176 @@
         <v>1.56</v>
       </c>
       <c r="X49" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ49" t="n">
         <v>15.5</v>
       </c>
-      <c r="Z49" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC49" t="n">
+      <c r="BA49" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BJ49" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD49" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV49" t="n">
+      <c r="BK49" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>22</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW49" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX49" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY49" t="n">
         <v>8.4</v>
       </c>
-      <c r="AW49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG49" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI49" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BJ49" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BK49" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BL49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM49" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BN49" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BO49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BP49" t="n">
-        <v>30</v>
-      </c>
-      <c r="BQ49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BR49" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS49" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BT49" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BU49" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BV49" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW49" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BX49" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY49" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BZ49" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="CA49" t="n">
-        <v>1.7</v>
+        <v>8</v>
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -13079,13 +13079,13 @@
         <v>1.3</v>
       </c>
       <c r="P50" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="Q50" t="n">
         <v>1.94</v>
       </c>
       <c r="R50" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S50" t="n">
         <v>3.25</v>
@@ -13094,7 +13094,7 @@
         <v>1.6</v>
       </c>
       <c r="U50" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V50" t="n">
         <v>1.6</v>
@@ -13109,7 +13109,7 @@
         <v>1000</v>
       </c>
       <c r="Z50" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AA50" t="n">
         <v>1000</v>
@@ -13118,13 +13118,13 @@
         <v>1000</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD50" t="n">
         <v>1000</v>
       </c>
       <c r="AE50" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF50" t="n">
         <v>1000</v>
@@ -13133,7 +13133,7 @@
         <v>1000</v>
       </c>
       <c r="AH50" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI50" t="n">
         <v>1000</v>
@@ -13142,7 +13142,7 @@
         <v>1000</v>
       </c>
       <c r="AK50" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL50" t="n">
         <v>1000</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -13327,13 +13327,13 @@
         <v>1.07</v>
       </c>
       <c r="N51" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="O51" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P51" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q51" t="n">
         <v>2.06</v>
@@ -13345,7 +13345,7 @@
         <v>3.75</v>
       </c>
       <c r="T51" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U51" t="n">
         <v>2.04</v>
@@ -13372,7 +13372,7 @@
         <v>1000</v>
       </c>
       <c r="AC51" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD51" t="n">
         <v>1000</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="G52" t="n">
         <v>970</v>
@@ -13572,7 +13572,7 @@
         <v>5.3</v>
       </c>
       <c r="K52" t="n">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -13581,7 +13581,7 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>1.1</v>
@@ -13614,7 +13614,7 @@
         <v>1000</v>
       </c>
       <c r="Y52" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Z52" t="n">
         <v>1000</v>
@@ -13728,59 +13728,59 @@
         <v>1000</v>
       </c>
       <c r="BK52" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BL52" t="n">
         <v>1000</v>
       </c>
       <c r="BM52" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BN52" t="n">
         <v>1000</v>
       </c>
       <c r="BO52" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BP52" t="n">
         <v>1000</v>
       </c>
       <c r="BQ52" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BR52" t="n">
         <v>1000</v>
       </c>
       <c r="BS52" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BT52" t="n">
         <v>1000</v>
       </c>
       <c r="BU52" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BV52" t="n">
         <v>1000</v>
       </c>
       <c r="BW52" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BX52" t="n">
         <v>1000</v>
       </c>
       <c r="BY52" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="BZ52" t="n">
         <v>1000</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -13835,28 +13835,28 @@
         <v>1.02</v>
       </c>
       <c r="N53" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="O53" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P53" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="R53" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S53" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="T53" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="U53" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="V53" t="n">
         <v>1.24</v>
@@ -13865,176 +13865,176 @@
         <v>2.2</v>
       </c>
       <c r="X53" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y53" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="Z53" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA53" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB53" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD53" t="n">
         <v>20</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AE53" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV53" t="n">
         <v>16</v>
       </c>
-      <c r="AD53" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF53" t="n">
+      <c r="AW53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD53" t="n">
         <v>20</v>
       </c>
-      <c r="AG53" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB53" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC53" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD53" t="n">
-        <v>15</v>
-      </c>
       <c r="BE53" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG53" t="n">
         <v>1.01</v>
       </c>
       <c r="BH53" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI53" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BJ53" t="n">
         <v>12</v>
       </c>
       <c r="BK53" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BL53" t="n">
         <v>1000</v>
       </c>
       <c r="BM53" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BN53" t="n">
         <v>6.6</v>
       </c>
       <c r="BO53" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BP53" t="n">
         <v>15</v>
       </c>
       <c r="BQ53" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BR53" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BS53" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BT53" t="n">
         <v>11.5</v>
       </c>
       <c r="BU53" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BV53" t="n">
         <v>44</v>
       </c>
       <c r="BW53" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BX53" t="n">
         <v>46</v>
       </c>
       <c r="BY53" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BZ53" t="n">
         <v>1000</v>
       </c>
       <c r="CA53" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -14071,10 +14071,10 @@
         <v>2.48</v>
       </c>
       <c r="H54" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I54" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J54" t="n">
         <v>3.4</v>
@@ -14098,13 +14098,13 @@
         <v>2.04</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R54" t="n">
         <v>1.39</v>
       </c>
       <c r="S54" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T54" t="n">
         <v>1.72</v>
@@ -14119,10 +14119,10 @@
         <v>1.67</v>
       </c>
       <c r="X54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y54" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z54" t="n">
         <v>24</v>
@@ -14131,16 +14131,16 @@
         <v>55</v>
       </c>
       <c r="AB54" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC54" t="n">
         <v>9.4</v>
       </c>
       <c r="AD54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE54" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF54" t="n">
         <v>17.5</v>
@@ -14152,16 +14152,16 @@
         <v>970</v>
       </c>
       <c r="AI54" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ54" t="n">
         <v>32</v>
       </c>
       <c r="AK54" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL54" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM54" t="n">
         <v>75</v>
@@ -14170,7 +14170,7 @@
         <v>20</v>
       </c>
       <c r="AO54" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AP54" t="n">
         <v>13</v>
@@ -14182,7 +14182,7 @@
         <v>20</v>
       </c>
       <c r="AS54" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT54" t="n">
         <v>9.6</v>
@@ -14191,13 +14191,13 @@
         <v>7.6</v>
       </c>
       <c r="AV54" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW54" t="n">
         <v>30</v>
       </c>
       <c r="AX54" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AY54" t="n">
         <v>10</v>
@@ -14206,25 +14206,25 @@
         <v>14</v>
       </c>
       <c r="BA54" t="n">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BB54" t="n">
         <v>28</v>
       </c>
       <c r="BC54" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BD54" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF54" t="n">
         <v>6.8</v>
       </c>
-      <c r="BE54" t="n">
+      <c r="BG54" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BF54" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG54" t="n">
-        <v>6.8</v>
       </c>
       <c r="BH54" t="n">
         <v>3.7</v>
@@ -14236,16 +14236,16 @@
         <v>9.6</v>
       </c>
       <c r="BK54" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL54" t="n">
         <v>1000</v>
       </c>
       <c r="BM54" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN54" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO54" t="n">
         <v>4.1</v>
@@ -14254,13 +14254,13 @@
         <v>1000</v>
       </c>
       <c r="BQ54" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR54" t="n">
         <v>1000</v>
       </c>
       <c r="BS54" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BT54" t="n">
         <v>6.6</v>
@@ -14272,23 +14272,23 @@
         <v>1000</v>
       </c>
       <c r="BW54" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX54" t="n">
         <v>1000</v>
       </c>
       <c r="BY54" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ54" t="n">
         <v>1000</v>
       </c>
       <c r="CA54" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
         <v>3.2</v>
       </c>
       <c r="I55" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>3.4</v>
@@ -14343,28 +14343,28 @@
         <v>1.07</v>
       </c>
       <c r="N55" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="O55" t="n">
         <v>1.31</v>
       </c>
       <c r="P55" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R55" t="n">
         <v>1.37</v>
       </c>
       <c r="S55" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T55" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U55" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V55" t="n">
         <v>1.43</v>
@@ -14406,7 +14406,7 @@
         <v>16.5</v>
       </c>
       <c r="AI55" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ55" t="n">
         <v>38</v>
@@ -14415,10 +14415,10 @@
         <v>26</v>
       </c>
       <c r="AL55" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM55" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN55" t="n">
         <v>21</v>
@@ -14472,31 +14472,31 @@
         <v>34</v>
       </c>
       <c r="BE55" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF55" t="n">
         <v>17.5</v>
       </c>
       <c r="BG55" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH55" t="n">
         <v>3.4</v>
       </c>
       <c r="BI55" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ55" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK55" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BL55" t="n">
         <v>1000</v>
       </c>
       <c r="BM55" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN55" t="n">
         <v>5.5</v>
@@ -14514,25 +14514,25 @@
         <v>1000</v>
       </c>
       <c r="BS55" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT55" t="n">
         <v>6.6</v>
       </c>
       <c r="BU55" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BV55" t="n">
         <v>1000</v>
       </c>
       <c r="BW55" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BX55" t="n">
         <v>1000</v>
       </c>
       <c r="BY55" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ55" t="n">
         <v>1000</v>
@@ -14542,14 +14542,14 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -14559,251 +14559,251 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Asociacion Deportiva Tarma</t>
+          <t>Osters</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cusco FC</t>
+          <t>Norrby IF</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P56" t="n">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ56" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -14813,251 +14813,251 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Paris St-G</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Progreso</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.97</v>
+        <v>2.42</v>
       </c>
       <c r="G57" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="H57" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="I57" t="n">
-        <v>5.6</v>
+        <v>3.35</v>
       </c>
       <c r="J57" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K57" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P57" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="Q57" t="n">
         <v>2.06</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO57" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA57" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG57" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BI57" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BJ57" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BK57" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BL57" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BM57" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BN57" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO57" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BP57" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BQ57" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BR57" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BS57" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BT57" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BU57" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BV57" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BW57" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX57" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BY57" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BZ57" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="CA57" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -15067,251 +15067,251 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Asociacion Deportiva Tarma</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Cusco FC</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="G58" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="H58" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I58" t="n">
-        <v>3.65</v>
+        <v>970</v>
       </c>
       <c r="J58" t="n">
-        <v>2.92</v>
+        <v>1.72</v>
       </c>
       <c r="K58" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P58" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.44</v>
+        <v>1.73</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -15321,251 +15321,251 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Progreso</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.34</v>
+        <v>1.97</v>
       </c>
       <c r="G59" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="H59" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="J59" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K59" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="L59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.58</v>
+        <v>2.06</v>
       </c>
       <c r="R59" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AJ59" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AK59" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AL59" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM59" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AN59" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AO59" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AQ59" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AR59" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AS59" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AT59" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AU59" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV59" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AW59" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AX59" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY59" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ59" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BA59" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BC59" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BD59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BE59" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BG59" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BH59" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BI59" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BJ59" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK59" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BL59" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM59" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BN59" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BO59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP59" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BQ59" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BR59" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BT59" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BU59" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BV59" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW59" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BX59" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY59" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BZ59" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA59" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -15580,31 +15580,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HFX Wanderers</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="G60" t="n">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="H60" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="I60" t="n">
-        <v>2.88</v>
+        <v>3.65</v>
       </c>
       <c r="J60" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="K60" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -15619,10 +15619,10 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.93</v>
+        <v>2.48</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -15812,14 +15812,14 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -15834,246 +15834,246 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colo Colo</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F61" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H61" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I61" t="n">
         <v>4.1</v>
       </c>
-      <c r="G61" t="n">
+      <c r="J61" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W61" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X61" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB61" t="n">
         <v>4.7</v>
       </c>
-      <c r="H61" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J61" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K61" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>0</v>
-      </c>
       <c r="BC61" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BD61" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE61" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BF61" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG61" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH61" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BI61" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BJ61" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK61" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BL61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM61" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BN61" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BO61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BP61" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BQ61" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BR61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS61" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT61" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BU61" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BV61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW61" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY61" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BZ61" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA61" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Canadian Premier League</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -16088,31 +16088,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>HFX Wanderers</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G62" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="H62" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="I62" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="J62" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K62" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -16127,10 +16127,10 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -16320,14 +16320,14 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -16337,36 +16337,36 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Juan Pablo II College</t>
+          <t>Colo Colo</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -16381,10 +16381,10 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -16574,14 +16574,14 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -16591,36 +16591,36 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fortaleza EC</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -16635,10 +16635,10 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.25</v>
+        <v>1.99</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -16828,14 +16828,14 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Peruvian Primera Division</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -16845,36 +16845,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Deportivo Garcilaso</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Deportes Concepcion</t>
+          <t>Juan Pablo II College</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -16889,10 +16889,10 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -17082,14 +17082,14 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Canadian Premier League</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -17099,36 +17099,36 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Atletico Ottawa</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -17143,10 +17143,10 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -17336,14 +17336,14 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Peruvian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -17353,36 +17353,36 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sport Boys (Per)</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Comerciantes Unidos</t>
+          <t>Deportes Concepcion</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="G67" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="H67" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="I67" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -17397,10 +17397,10 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -17590,261 +17590,769 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-28 13:03:17</t>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Atletico Ottawa</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K68" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB68" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:47:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Peruvian Primera Division</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sport Boys (Per)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H69" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I69" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB69" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:47:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Sport Recife</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Nautico PE</t>
         </is>
       </c>
-      <c r="F68" t="n">
+      <c r="F70" t="n">
         <v>1.41</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G70" t="n">
         <v>100</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H70" t="n">
         <v>1.41</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I70" t="n">
         <v>100</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J70" t="n">
         <v>1.09</v>
       </c>
-      <c r="K68" t="n">
+      <c r="K70" t="n">
         <v>6.8</v>
       </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY68" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB68" t="inlineStr">
-        <is>
-          <t>2026-05-28 13:03:17</t>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB70" t="inlineStr">
+        <is>
+          <t>2026-05-28 14:47:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-05-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-05-30.xlsx
@@ -860,7 +860,7 @@
         <v>4.2</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="H2" t="n">
         <v>1.82</v>
@@ -881,7 +881,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.26</v>
@@ -893,7 +893,7 @@
         <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>2.96</v>
@@ -1022,7 +1022,7 @@
         <v>3.8</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -1135,10 +1135,10 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
         <v>1.85</v>
@@ -1276,7 +1276,7 @@
         <v>3.3</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
         <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.28</v>
@@ -1643,34 +1643,34 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="T5" t="n">
         <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V5" t="n">
         <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
         <v>24</v>
@@ -1685,13 +1685,13 @@
         <v>55</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
         <v>36</v>
@@ -1700,16 +1700,16 @@
         <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI5" t="n">
         <v>44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
         <v>28</v>
@@ -1721,34 +1721,34 @@
         <v>80</v>
       </c>
       <c r="AN5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO5" t="n">
         <v>27</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>40</v>
       </c>
       <c r="AT5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.6</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
         <v>14.5</v>
@@ -1760,25 +1760,25 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.8</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
         <v>20</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BE5" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="BF5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BH5" t="n">
         <v>4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -1903,13 +1903,13 @@
         <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
         <v>3.5</v>
@@ -1918,10 +1918,10 @@
         <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
         <v>1.67</v>
@@ -2038,7 +2038,7 @@
         <v>3.45</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="BJ6" t="n">
         <v>10</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
         <v>5.5</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H7" t="n">
         <v>1.69</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="J7" t="n">
         <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.38</v>
@@ -2292,7 +2292,7 @@
         <v>3.25</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
@@ -2304,7 +2304,7 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H8" t="n">
         <v>3.15</v>
@@ -2396,7 +2396,7 @@
         <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
         <v>1.32</v>
@@ -2417,7 +2417,7 @@
         <v>1.79</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -2432,7 +2432,7 @@
         <v>1.41</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X8" t="n">
         <v>20</v>
@@ -2543,22 +2543,22 @@
         <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ8" t="n">
         <v>9.4</v>
       </c>
       <c r="BK8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN8" t="n">
         <v>5.6</v>
@@ -2576,7 +2576,7 @@
         <v>29</v>
       </c>
       <c r="BS8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BT8" t="n">
         <v>6.8</v>
@@ -2588,23 +2588,23 @@
         <v>26</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BZ8" t="n">
         <v>23</v>
       </c>
       <c r="CA8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -2638,10 +2638,10 @@
         <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I9" t="n">
         <v>2.94</v>
@@ -2650,7 +2650,7 @@
         <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2659,13 +2659,13 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O9" t="n">
         <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
         <v>1.84</v>
@@ -2800,7 +2800,7 @@
         <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.88</v>
+        <v>1.93</v>
       </c>
       <c r="BJ9" t="n">
         <v>12.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
         <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -3421,10 +3421,10 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>1.28</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -3651,16 +3651,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G13" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
@@ -3675,34 +3675,34 @@
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S13" t="n">
         <v>2.52</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X13" t="n">
         <v>28</v>
@@ -3774,7 +3774,7 @@
         <v>3.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="AV13" t="n">
         <v>12.5</v>
@@ -3807,7 +3807,7 @@
         <v>4.1</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG13" t="n">
         <v>3.95</v>
@@ -3822,13 +3822,13 @@
         <v>13</v>
       </c>
       <c r="BK13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BN13" t="n">
         <v>6.8</v>
@@ -3840,41 +3840,41 @@
         <v>17.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BR13" t="n">
         <v>30</v>
       </c>
       <c r="BS13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BT13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU13" t="n">
         <v>5</v>
       </c>
       <c r="BV13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BX13" t="n">
         <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BZ13" t="n">
         <v>22</v>
       </c>
       <c r="CA13" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -3908,10 +3908,10 @@
         <v>1.75</v>
       </c>
       <c r="G14" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
         <v>7</v>
@@ -3929,7 +3929,7 @@
         <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="O14" t="n">
         <v>1.42</v>
@@ -3938,7 +3938,7 @@
         <v>1.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R14" t="n">
         <v>1.25</v>
@@ -3956,7 +3956,7 @@
         <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="X14" t="n">
         <v>13</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -4183,13 +4183,13 @@
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O15" t="n">
         <v>1.49</v>
       </c>
       <c r="P15" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q15" t="n">
         <v>2.62</v>
@@ -4198,7 +4198,7 @@
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="n">
         <v>2.08</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
         <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I16" t="n">
         <v>1.79</v>
@@ -4449,7 +4449,7 @@
         <v>1.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
         <v>3.3</v>
@@ -4458,7 +4458,7 @@
         <v>1.87</v>
       </c>
       <c r="U16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V16" t="n">
         <v>2.26</v>
@@ -4575,43 +4575,43 @@
         <v>9.6</v>
       </c>
       <c r="BH16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BJ16" t="n">
         <v>10.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BN16" t="n">
         <v>9</v>
       </c>
       <c r="BO16" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU16" t="n">
         <v>3.5</v>
@@ -4620,23 +4620,23 @@
         <v>12</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX16" t="n">
         <v>27</v>
       </c>
       <c r="BY16" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ16" t="n">
         <v>22</v>
       </c>
       <c r="CA16" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -4670,13 +4670,13 @@
         <v>2.24</v>
       </c>
       <c r="G17" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H17" t="n">
         <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J17" t="n">
         <v>3.15</v>
@@ -4718,7 +4718,7 @@
         <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -4739,7 +4739,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -4748,7 +4748,7 @@
         <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH17" t="n">
         <v>1000</v>
@@ -4775,58 +4775,58 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AR17" t="n">
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AU17" t="n">
         <v>5.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AX17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY17" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BC17" t="n">
         <v>18.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BH17" t="n">
         <v>3.3</v>
@@ -4856,7 +4856,7 @@
         <v>18.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BR17" t="n">
         <v>1000</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="CB17" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="G18" t="n">
         <v>3.9</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="CB18" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5178,7 @@
         <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H19" t="n">
         <v>5.1</v>
@@ -5226,7 +5226,7 @@
         <v>1.15</v>
       </c>
       <c r="W19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="CB19" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="CB20" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -5716,13 +5716,13 @@
         <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R21" t="n">
         <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="T21" t="n">
         <v>1.41</v>
@@ -5734,7 +5734,7 @@
         <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="X21" t="n">
         <v>30</v>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="CB21" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G22" t="n">
         <v>2.12</v>
@@ -5946,10 +5946,10 @@
         <v>3.4</v>
       </c>
       <c r="I22" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
         <v>4.5</v>
@@ -5958,10 +5958,10 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.15</v>
@@ -5970,19 +5970,19 @@
         <v>2.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S22" t="n">
         <v>2.18</v>
       </c>
       <c r="T22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U22" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="V22" t="n">
         <v>1.38</v>
@@ -6093,7 +6093,7 @@
         <v>7.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG22" t="n">
         <v>14</v>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="CB22" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -6194,16 +6194,16 @@
         <v>1.74</v>
       </c>
       <c r="G23" t="n">
-        <v>240</v>
+        <v>970</v>
       </c>
       <c r="H23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="I23" t="n">
         <v>4.8</v>
       </c>
       <c r="J23" t="n">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="K23" t="n">
         <v>950</v>
@@ -6239,10 +6239,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -6475,22 +6475,22 @@
         <v>1.16</v>
       </c>
       <c r="P24" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S24" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V24" t="n">
         <v>1.06</v>
@@ -6547,22 +6547,22 @@
         <v>200</v>
       </c>
       <c r="AN24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AO24" t="n">
         <v>330</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT24" t="n">
         <v>8.4</v>
@@ -6571,40 +6571,40 @@
         <v>12</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AY24" t="n">
         <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC24" t="n">
         <v>10</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH24" t="n">
         <v>1000</v>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="CB24" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -6699,22 +6699,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G25" t="n">
         <v>4.5</v>
       </c>
       <c r="H25" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="I25" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -6723,13 +6723,13 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O25" t="n">
         <v>1.3</v>
       </c>
       <c r="P25" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q25" t="n">
         <v>1.88</v>
@@ -6741,7 +6741,7 @@
         <v>3.25</v>
       </c>
       <c r="T25" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U25" t="n">
         <v>2.12</v>
@@ -6882,7 +6882,7 @@
         <v>10.5</v>
       </c>
       <c r="BO25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP25" t="n">
         <v>48</v>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="CB25" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
         <v>1.63</v>
       </c>
       <c r="U26" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V26" t="n">
         <v>1.28</v>
@@ -7136,7 +7136,7 @@
         <v>6.4</v>
       </c>
       <c r="BO26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP26" t="n">
         <v>19</v>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="CB26" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="CB27" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
         <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R28" t="n">
         <v>1.33</v>
@@ -7518,19 +7518,19 @@
         <v>18</v>
       </c>
       <c r="Y28" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA28" t="n">
         <v>220</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD28" t="n">
         <v>29</v>
@@ -7539,25 +7539,25 @@
         <v>110</v>
       </c>
       <c r="AF28" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG28" t="n">
         <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI28" t="n">
         <v>110</v>
       </c>
       <c r="AJ28" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AK28" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL28" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM28" t="n">
         <v>160</v>
@@ -7572,13 +7572,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.4</v>
+        <v>40</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="AT28" t="n">
         <v>6</v>
@@ -7587,10 +7587,10 @@
         <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AX28" t="n">
         <v>7.2</v>
@@ -7599,28 +7599,28 @@
         <v>7.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BC28" t="n">
         <v>13</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF28" t="n">
         <v>7.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH28" t="n">
         <v>4</v>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="CB28" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q29" t="n">
         <v>2.24</v>
@@ -7938,7 +7938,7 @@
       </c>
       <c r="CB29" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="CB30" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="CB31" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
         <v>1.92</v>
       </c>
       <c r="G32" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H32" t="n">
         <v>4.4</v>
@@ -8492,7 +8492,7 @@
         <v>3.65</v>
       </c>
       <c r="K32" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.38</v>
@@ -8522,25 +8522,25 @@
         <v>1.86</v>
       </c>
       <c r="U32" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V32" t="n">
         <v>1.26</v>
       </c>
       <c r="W32" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y32" t="n">
         <v>15.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA32" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB32" t="n">
         <v>9.6</v>
@@ -8552,7 +8552,7 @@
         <v>18.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF32" t="n">
         <v>12</v>
@@ -8594,7 +8594,7 @@
         <v>29</v>
       </c>
       <c r="AS32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT32" t="n">
         <v>8.199999999999999</v>
@@ -8606,7 +8606,7 @@
         <v>16</v>
       </c>
       <c r="AW32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX32" t="n">
         <v>10.5</v>
@@ -8621,7 +8621,7 @@
         <v>55</v>
       </c>
       <c r="BB32" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC32" t="n">
         <v>18</v>
@@ -8630,13 +8630,13 @@
         <v>32</v>
       </c>
       <c r="BE32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF32" t="n">
         <v>11.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH32" t="n">
         <v>1000</v>
@@ -8648,7 +8648,7 @@
         <v>13.5</v>
       </c>
       <c r="BK32" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BL32" t="n">
         <v>1000</v>
@@ -8660,13 +8660,13 @@
         <v>5.9</v>
       </c>
       <c r="BO32" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP32" t="n">
         <v>18.5</v>
       </c>
       <c r="BQ32" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR32" t="n">
         <v>1000</v>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="CB32" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="CB33" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
         <v>2.02</v>
       </c>
       <c r="I34" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J34" t="n">
         <v>4</v>
@@ -9018,7 +9018,7 @@
         <v>2.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="R34" t="n">
         <v>1.25</v>
@@ -9033,7 +9033,7 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W34" t="n">
         <v>1.34</v>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="CB35" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9562,7 @@
         <v>14</v>
       </c>
       <c r="AC36" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD36" t="n">
         <v>40</v>
@@ -9571,7 +9571,7 @@
         <v>130</v>
       </c>
       <c r="AF36" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG36" t="n">
         <v>13</v>
@@ -9604,13 +9604,13 @@
         <v>20</v>
       </c>
       <c r="AQ36" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AS36" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT36" t="n">
         <v>8.6</v>
@@ -9619,10 +9619,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV36" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AX36" t="n">
         <v>8.800000000000001</v>
@@ -9634,7 +9634,7 @@
         <v>16.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB36" t="n">
         <v>9.4</v>
@@ -9646,13 +9646,13 @@
         <v>21</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF36" t="n">
         <v>3.7</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BH36" t="n">
         <v>4.8</v>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="CB36" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -9762,10 +9762,10 @@
         <v>4.5</v>
       </c>
       <c r="K37" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
         <v>1.05</v>
@@ -9777,7 +9777,7 @@
         <v>1.26</v>
       </c>
       <c r="P37" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q37" t="n">
         <v>1.76</v>
@@ -9849,7 +9849,7 @@
         <v>150</v>
       </c>
       <c r="AN37" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO37" t="n">
         <v>140</v>
@@ -9861,10 +9861,10 @@
         <v>20</v>
       </c>
       <c r="AR37" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT37" t="n">
         <v>8</v>
@@ -9873,10 +9873,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AX37" t="n">
         <v>8.4</v>
@@ -9888,7 +9888,7 @@
         <v>20</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB37" t="n">
         <v>12.5</v>
@@ -9897,16 +9897,16 @@
         <v>14</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BF37" t="n">
         <v>6.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BH37" t="n">
         <v>1000</v>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="CB37" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="CB38" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -10279,13 +10279,13 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="O39" t="n">
         <v>1.2</v>
       </c>
       <c r="P39" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q39" t="n">
         <v>1.2</v>
@@ -10294,7 +10294,7 @@
         <v>1.24</v>
       </c>
       <c r="S39" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="CB39" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
         <v>1.24</v>
       </c>
       <c r="S40" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="CB40" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -10787,13 +10787,13 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="O41" t="n">
         <v>1.18</v>
       </c>
       <c r="P41" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="Q41" t="n">
         <v>1.18</v>
@@ -10802,7 +10802,7 @@
         <v>1.24</v>
       </c>
       <c r="S41" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="T41" t="n">
         <v>1.01</v>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="CB41" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -11041,13 +11041,13 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="O42" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="P42" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q42" t="n">
         <v>1.24</v>
@@ -11056,7 +11056,7 @@
         <v>1.24</v>
       </c>
       <c r="S42" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="T42" t="n">
         <v>1.01</v>
@@ -11240,7 +11240,7 @@
       </c>
       <c r="CB42" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -11295,13 +11295,13 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="O43" t="n">
         <v>1.16</v>
       </c>
       <c r="P43" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q43" t="n">
         <v>1.16</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="CB43" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -11748,7 +11748,7 @@
       </c>
       <c r="CB44" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -11785,13 +11785,13 @@
         <v>1000</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="J45" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="K45" t="n">
         <v>1000</v>
@@ -11827,10 +11827,10 @@
         <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>1.2</v>
+        <v>1.69</v>
       </c>
       <c r="W45" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -12002,7 +12002,7 @@
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
         <v>1.72</v>
       </c>
       <c r="R46" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="S46" t="n">
         <v>2.72</v>
@@ -12256,7 +12256,7 @@
       </c>
       <c r="CB46" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -12290,7 +12290,7 @@
         <v>2.86</v>
       </c>
       <c r="G47" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="H47" t="n">
         <v>2.16</v>
@@ -12311,22 +12311,22 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="O47" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="P47" t="n">
         <v>2.66</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R47" t="n">
         <v>1.27</v>
       </c>
       <c r="S47" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -12338,7 +12338,7 @@
         <v>1.7</v>
       </c>
       <c r="W47" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X47" t="n">
         <v>36</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="CB47" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -12550,10 +12550,10 @@
         <v>1.23</v>
       </c>
       <c r="I48" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="J48" t="n">
-        <v>5.1</v>
+        <v>2.34</v>
       </c>
       <c r="K48" t="n">
         <v>100</v>
@@ -12586,7 +12586,7 @@
         <v>1.66</v>
       </c>
       <c r="U48" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V48" t="n">
         <v>3.75</v>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="CB48" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13018,7 @@
       </c>
       <c r="CB49" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
         <v>3.25</v>
       </c>
       <c r="H50" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I50" t="n">
         <v>2.66</v>
@@ -13272,7 +13272,7 @@
       </c>
       <c r="CB50" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -13414,7 +13414,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ51" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR51" t="n">
         <v>1.01</v>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="CB51" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13780,7 @@
       </c>
       <c r="CB52" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -13829,7 +13829,7 @@
         <v>3.5</v>
       </c>
       <c r="L53" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M53" t="n">
         <v>1.08</v>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="CB53" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
         <v>2.46</v>
       </c>
       <c r="G54" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H54" t="n">
         <v>3.2</v>
@@ -14083,40 +14083,40 @@
         <v>3.45</v>
       </c>
       <c r="L54" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M54" t="n">
         <v>1.07</v>
       </c>
       <c r="N54" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O54" t="n">
         <v>1.33</v>
       </c>
       <c r="P54" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q54" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R54" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S54" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="T54" t="n">
         <v>1.78</v>
       </c>
       <c r="U54" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V54" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W54" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X54" t="n">
         <v>13.5</v>
@@ -14134,13 +14134,13 @@
         <v>11</v>
       </c>
       <c r="AC54" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD54" t="n">
         <v>16</v>
       </c>
       <c r="AE54" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AF54" t="n">
         <v>15.5</v>
@@ -14149,28 +14149,28 @@
         <v>13</v>
       </c>
       <c r="AH54" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI54" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ54" t="n">
         <v>36</v>
       </c>
       <c r="AK54" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL54" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM54" t="n">
         <v>90</v>
       </c>
       <c r="AN54" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO54" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP54" t="n">
         <v>11</v>
@@ -14182,19 +14182,19 @@
         <v>18.5</v>
       </c>
       <c r="AS54" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT54" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU54" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV54" t="n">
         <v>13.5</v>
       </c>
       <c r="AW54" t="n">
-        <v>30</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX54" t="n">
         <v>13.5</v>
@@ -14203,34 +14203,34 @@
         <v>11</v>
       </c>
       <c r="AZ54" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA54" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB54" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BC54" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD54" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE54" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF54" t="n">
-        <v>19.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG54" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="BH54" t="n">
         <v>3.6</v>
       </c>
       <c r="BI54" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="BJ54" t="n">
         <v>9.6</v>
@@ -14288,7 +14288,7 @@
       </c>
       <c r="CB54" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -14406,7 +14406,7 @@
         <v>18.5</v>
       </c>
       <c r="AI55" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ55" t="n">
         <v>38</v>
@@ -14418,7 +14418,7 @@
         <v>42</v>
       </c>
       <c r="AM55" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN55" t="n">
         <v>22</v>
@@ -14472,7 +14472,7 @@
         <v>36</v>
       </c>
       <c r="BE55" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF55" t="n">
         <v>19</v>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="CB55" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -14579,16 +14579,16 @@
         <v>2.2</v>
       </c>
       <c r="H56" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J56" t="n">
         <v>3.9</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="L56" t="n">
         <v>1.01</v>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="CB57" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -15081,10 +15081,10 @@
         </is>
       </c>
       <c r="F58" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G58" t="n">
         <v>2.44</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2.46</v>
       </c>
       <c r="H58" t="n">
         <v>3.3</v>
@@ -15105,37 +15105,37 @@
         <v>1.08</v>
       </c>
       <c r="N58" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="O58" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P58" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R58" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S58" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T58" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U58" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V58" t="n">
         <v>1.42</v>
       </c>
       <c r="W58" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X58" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y58" t="n">
         <v>12</v>
@@ -15153,10 +15153,10 @@
         <v>7.6</v>
       </c>
       <c r="AD58" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE58" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF58" t="n">
         <v>14</v>
@@ -15177,16 +15177,16 @@
         <v>25</v>
       </c>
       <c r="AL58" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM58" t="n">
         <v>90</v>
       </c>
       <c r="AN58" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AO58" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP58" t="n">
         <v>12</v>
@@ -15195,7 +15195,7 @@
         <v>11.5</v>
       </c>
       <c r="AR58" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS58" t="n">
         <v>50</v>
@@ -15210,7 +15210,7 @@
         <v>14</v>
       </c>
       <c r="AW58" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX58" t="n">
         <v>13.5</v>
@@ -15219,7 +15219,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ58" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA58" t="n">
         <v>46</v>
@@ -15231,7 +15231,7 @@
         <v>23</v>
       </c>
       <c r="BD58" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE58" t="n">
         <v>80</v>
@@ -15240,7 +15240,7 @@
         <v>16</v>
       </c>
       <c r="BG58" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH58" t="n">
         <v>3.25</v>
@@ -15252,7 +15252,7 @@
         <v>9.4</v>
       </c>
       <c r="BK58" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL58" t="n">
         <v>120</v>
@@ -15270,13 +15270,13 @@
         <v>17.5</v>
       </c>
       <c r="BQ58" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BR58" t="n">
         <v>30</v>
       </c>
       <c r="BS58" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BT58" t="n">
         <v>6.4</v>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="CB58" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -15558,7 +15558,7 @@
       </c>
       <c r="CB59" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -15592,7 +15592,7 @@
         <v>1.97</v>
       </c>
       <c r="G60" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="H60" t="n">
         <v>4.1</v>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="CB60" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -15846,10 +15846,10 @@
         <v>2.5</v>
       </c>
       <c r="G61" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="H61" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="I61" t="n">
         <v>3.15</v>
@@ -15879,7 +15879,7 @@
         <v>1.87</v>
       </c>
       <c r="R61" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S61" t="n">
         <v>3.5</v>
@@ -16066,7 +16066,7 @@
       </c>
       <c r="CB61" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16097,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="G62" t="n">
         <v>3.4</v>
@@ -16112,7 +16112,7 @@
         <v>3.2</v>
       </c>
       <c r="K62" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="L62" t="n">
         <v>1.01</v>
@@ -16136,7 +16136,7 @@
         <v>1.26</v>
       </c>
       <c r="S62" t="n">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
       <c r="T62" t="n">
         <v>1.52</v>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="CB62" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16402,7 @@
         <v>1.36</v>
       </c>
       <c r="W63" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X63" t="n">
         <v>13.5</v>
@@ -16574,7 +16574,7 @@
       </c>
       <c r="CB63" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="CB64" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -16883,7 +16883,7 @@
         <v>1.12</v>
       </c>
       <c r="N65" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="O65" t="n">
         <v>1.52</v>
@@ -16907,7 +16907,7 @@
         <v>1.78</v>
       </c>
       <c r="V65" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W65" t="n">
         <v>1.62</v>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="CB65" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -17137,7 +17137,7 @@
         <v>1.06</v>
       </c>
       <c r="N66" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O66" t="n">
         <v>1.28</v>
@@ -17336,7 +17336,7 @@
       </c>
       <c r="CB66" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -17385,10 +17385,10 @@
         <v>3.85</v>
       </c>
       <c r="L67" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M67" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N67" t="n">
         <v>3</v>
@@ -17397,16 +17397,16 @@
         <v>1.42</v>
       </c>
       <c r="P67" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q67" t="n">
         <v>2.26</v>
       </c>
       <c r="R67" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S67" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T67" t="n">
         <v>2.06</v>
@@ -17475,7 +17475,7 @@
         <v>140</v>
       </c>
       <c r="AP67" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ67" t="n">
         <v>11</v>
@@ -17490,10 +17490,10 @@
         <v>5.5</v>
       </c>
       <c r="AU67" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV67" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW67" t="n">
         <v>5.6</v>
@@ -17590,7 +17590,7 @@
       </c>
       <c r="CB67" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -17645,7 +17645,7 @@
         <v>1.09</v>
       </c>
       <c r="N68" t="n">
-        <v>1.59</v>
+        <v>1.05</v>
       </c>
       <c r="O68" t="n">
         <v>1.1</v>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="CB68" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -17899,7 +17899,7 @@
         <v>1.1</v>
       </c>
       <c r="N69" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="O69" t="n">
         <v>1.46</v>
@@ -17908,7 +17908,7 @@
         <v>1.53</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R69" t="n">
         <v>1.22</v>
@@ -17923,7 +17923,7 @@
         <v>1.84</v>
       </c>
       <c r="V69" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W69" t="n">
         <v>1.66</v>
@@ -18040,7 +18040,7 @@
         <v>2.94</v>
       </c>
       <c r="BI69" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="BJ69" t="n">
         <v>1000</v>
@@ -18055,7 +18055,7 @@
         <v>1.05</v>
       </c>
       <c r="BN69" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BO69" t="n">
         <v>3.65</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="CB69" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -18352,7 +18352,7 @@
       </c>
       <c r="CB70" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -18386,19 +18386,19 @@
         <v>1.65</v>
       </c>
       <c r="G71" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H71" t="n">
         <v>5.1</v>
       </c>
       <c r="I71" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J71" t="n">
         <v>3.8</v>
       </c>
       <c r="K71" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -18431,10 +18431,10 @@
         <v>1.81</v>
       </c>
       <c r="V71" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W71" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X71" t="n">
         <v>28</v>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="CB71" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -18655,13 +18655,13 @@
         <v>4</v>
       </c>
       <c r="L72" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M72" t="n">
         <v>1.05</v>
       </c>
       <c r="N72" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O72" t="n">
         <v>1.24</v>
@@ -18676,7 +18676,7 @@
         <v>1.47</v>
       </c>
       <c r="S72" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="T72" t="n">
         <v>1.67</v>
@@ -18709,7 +18709,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD72" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE72" t="n">
         <v>55</v>
@@ -18781,13 +18781,13 @@
         <v>5.2</v>
       </c>
       <c r="BB72" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC72" t="n">
         <v>4.6</v>
       </c>
       <c r="BD72" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE72" t="n">
         <v>5.4</v>
@@ -18860,7 +18860,7 @@
       </c>
       <c r="CB72" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -18939,7 +18939,7 @@
         <v>1.89</v>
       </c>
       <c r="V73" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W73" t="n">
         <v>1.54</v>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="CB73" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -19169,7 +19169,7 @@
         <v>1.01</v>
       </c>
       <c r="N74" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="O74" t="n">
         <v>1.28</v>
@@ -19181,7 +19181,7 @@
         <v>1.87</v>
       </c>
       <c r="R74" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S74" t="n">
         <v>1.87</v>
@@ -19368,7 +19368,7 @@
       </c>
       <c r="CB74" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -19402,16 +19402,16 @@
         <v>2.8</v>
       </c>
       <c r="G75" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="H75" t="n">
         <v>2.6</v>
       </c>
       <c r="I75" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="J75" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="K75" t="n">
         <v>950</v>
@@ -19423,10 +19423,10 @@
         <v>1.01</v>
       </c>
       <c r="N75" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="O75" t="n">
-        <v>1.51</v>
+        <v>1.02</v>
       </c>
       <c r="P75" t="n">
         <v>1.25</v>
@@ -19444,13 +19444,13 @@
         <v>1.01</v>
       </c>
       <c r="U75" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V75" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W75" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="X75" t="n">
         <v>9.6</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="CB75" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -19653,7 +19653,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G76" t="n">
         <v>1.61</v>
@@ -19692,7 +19692,7 @@
         <v>1.32</v>
       </c>
       <c r="S76" t="n">
-        <v>1.94</v>
+        <v>3.15</v>
       </c>
       <c r="T76" t="n">
         <v>1.89</v>
@@ -19719,7 +19719,7 @@
         <v>1000</v>
       </c>
       <c r="AB76" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC76" t="n">
         <v>1000</v>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="CB76" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -19943,7 +19943,7 @@
         <v>1.91</v>
       </c>
       <c r="R77" t="n">
-        <v>1.36</v>
+        <v>1.08</v>
       </c>
       <c r="S77" t="n">
         <v>1.91</v>
@@ -19970,7 +19970,7 @@
         <v>95</v>
       </c>
       <c r="AA77" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="AB77" t="n">
         <v>8.4</v>
@@ -19982,7 +19982,7 @@
         <v>42</v>
       </c>
       <c r="AE77" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF77" t="n">
         <v>9</v>
@@ -20012,7 +20012,7 @@
         <v>8.6</v>
       </c>
       <c r="AO77" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AP77" t="n">
         <v>11</v>
@@ -20090,7 +20090,7 @@
         <v>4.9</v>
       </c>
       <c r="BO77" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="BP77" t="n">
         <v>11.5</v>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="CB77" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -20164,19 +20164,19 @@
         <v>4.1</v>
       </c>
       <c r="G78" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H78" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="I78" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="J78" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K78" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L78" t="n">
         <v>1.01</v>
@@ -20185,22 +20185,22 @@
         <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="O78" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P78" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="R78" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="S78" t="n">
-        <v>2.84</v>
+        <v>1.92</v>
       </c>
       <c r="T78" t="n">
         <v>1.01</v>
@@ -20209,10 +20209,10 @@
         <v>1.01</v>
       </c>
       <c r="V78" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="W78" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="X78" t="n">
         <v>1000</v>
@@ -20323,7 +20323,7 @@
         <v>1.01</v>
       </c>
       <c r="BH78" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI78" t="n">
         <v>2.76</v>
@@ -20384,7 +20384,7 @@
       </c>
       <c r="CB78" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -20445,16 +20445,16 @@
         <v>1.59</v>
       </c>
       <c r="P79" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="R79" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S79" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="T79" t="n">
         <v>2.32</v>
@@ -20580,7 +20580,7 @@
         <v>2.66</v>
       </c>
       <c r="BI79" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="BJ79" t="n">
         <v>13.5</v>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="CB79" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
         <v>1.68</v>
       </c>
       <c r="G80" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H80" t="n">
         <v>5.9</v>
@@ -20681,218 +20681,218 @@
         <v>7.6</v>
       </c>
       <c r="J80" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K80" t="n">
         <v>4</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P80" t="n">
         <v>1.73</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB80" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG80" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI80" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BJ80" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BK80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BL80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM80" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BN80" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BO80" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BP80" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BQ80" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BR80" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BS80" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BT80" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BU80" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BV80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BX80" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY80" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BZ80" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA80" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="CB80" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -20935,7 +20935,7 @@
         <v>5.6</v>
       </c>
       <c r="J81" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K81" t="n">
         <v>3.9</v>
@@ -21146,7 +21146,7 @@
       </c>
       <c r="CB81" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
@@ -21177,230 +21177,230 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1.41</v>
+        <v>2.32</v>
       </c>
       <c r="G82" t="n">
-        <v>100</v>
+        <v>2.54</v>
       </c>
       <c r="H82" t="n">
-        <v>1.41</v>
+        <v>3.55</v>
       </c>
       <c r="I82" t="n">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="J82" t="n">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="K82" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P82" t="n">
         <v>1.84</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG82" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI82" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BJ82" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK82" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BL82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM82" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BN82" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO82" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BP82" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BQ82" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BR82" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BS82" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BT82" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BV82" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BW82" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BX82" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY82" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BZ82" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="CA82" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="CB82" t="inlineStr">
         <is>
-          <t>2026-05-28 19:29:09</t>
+          <t>2026-05-28 21:50:56</t>
         </is>
       </c>
     </row>
